--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0103.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0103.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Cấu hình phần thưởng không tồn tại</t>
+          <t>Cấu hình phần thưởng không tồn tại.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Có ID vật phẩm không hợp lệ</t>
+          <t>ID Vật Phẩm Không Hợp Lệ</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Có loại vật phẩm không hợp lệ</t>
+          <t>Loại Vật Phẩm Không Hợp Lệ</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Chưa đáp ứng điều kiện lên cấp</t>
+          <t>Chưa đủ điều kiện nâng cấp</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Kinh nghiệm (EXP) không đủ để lên cấp</t>
+          <t>Kinh nghiệm không đủ để lên cấp.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Không có phần thưởng để nhận</t>
+          <t>Không có phần thưởng nào để nhận</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Đã đạt số lượng Waveplate tối đa</t>
+          <t>Đã đạt Giới Hạn Bản Waveplate</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Hiện không thể dịch chuyển</t>
+          <t>Hiện tại bạn không thể dịch chuyển.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Hiện không thể tham gia Co-op</t>
+          <t>Hiện không thể tham gia Chế Độ Hợp Tác</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Không thể điều chỉnh đội hình trong trạng thái hiện tại</t>
+          <t>Không thể thay đổi đội hình ở trạng thái hiện tại</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Đã đạt giới hạn Báo cáo hàng ngày</t>
+          <t>Đã đạt giới hạn Báo Cáo Hằng Ngày</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Lý do báo cáo không hợp lệ</t>
+          <t>Lý do Báo cáo không hợp lệ</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Văn bản báo cáo vượt quá giới hạn</t>
+          <t>Nội dung báo cáo vượt quá giới hạn</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Công cụ nấu ăn đã được sửa chữa</t>
+          <t>Đã sửa xong dụng cụ nấu ăn</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Cấp độ Đầu bếp không hợp lệ</t>
+          <t>Cấp Đầu Bếp không hợp lệ</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Chưa đủ điều kiện để lên cấp</t>
+          <t>Chưa đáp ứng điều kiện nâng cấp</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Cấu hình Tương tác không tồn tại</t>
+          <t>Không tìm thấy cấu hình tương tác</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Cấu hình Thử thách không tồn tại</t>
+          <t>Cấu hình thử thách không tồn tại</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Không có thông tin đội</t>
+          <t>Không có thông tin đội nhóm</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Số lượng thành viên trong đội không chính xác</t>
+          <t>Số lượng thành viên trong đội không đúng</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Không thể điều chỉnh đội hình cho giai đoạn này</t>
+          <t>Không thể thay đổi đội hình cho giai đoạn này</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Thử thách không khả dụng</t>
+          <t>Thách đấu chưa mở</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Số lượng nhân vật bị khóa cho Tháp Nghịch Cảnh vượt quá giới hạn</t>
+          <t>Số Cộng Hưởng Giả bị khóa cho Tháp Nghịch Cảnh đã vượt quá giới hạn</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Nhân vật bị khóa cho mục đích khác</t>
+          <t>{CharacterName} bị khóa vì lý do khác.</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Lấy thông tin nhân vật cho Forward Base thất bại</t>
+          <t>Không tải được nhân vật cho Forward Base</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Lấy thông tin đội cho Tháp Nghịch Cảnh thất bại</t>
+          <t>Không thể tải đội hình cho Tháp Nghịch Cảnh</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Lấy thông tin nhân vật cho Tháp Nghịch Cảnh thất bại</t>
+          <t>Không thể tải danh sách Cộng Hưởng Giả cho Tháp Nghịch Cảnh</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Lấy thông tin đội cho Tháp Nghịch Cảnh thất bại</t>
+          <t>Không thể tải đội hình cho Tháp Nghịch Cảnh</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Phe phái bị khóa</t>
+          <t>Phe phái đã bị khóa</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Không có phần thưởng Faction Influence để nhận</t>
+          <t>Không có phần thưởng Ảnh Hưởng Phe phái nào để nhận.</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Cấu hình Phe phái không tồn tại</t>
+          <t>Cấu hình phe phái không tồn tại</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Insufficient Influence</t>
+          <t>Ảnh hưởng không đủ</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Không thể nhận thưởng Ảnh Hưởng</t>
+          <t>Không thể nhận phần thưởng Ảnh Hưởng</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Hệ thống Bang Hội bị khóa</t>
+          <t>Hệ thống phe phái đã bị khóa</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Hệ thống Chế Tạo Vũ Khí không khả dụng</t>
+          <t>Hệ thống Chế Tạo Vũ Khí chưa mở</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Bản Thiết Kế Chế Tạo không khả dụng</t>
+          <t>Bản Thiết Kế chưa có sẵn</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Không tìm thấy cấu hình Chế Tạo</t>
+          <t>Không tìm thấy cấu hình chế tạo</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Bản Thiết Kế Chế Tạo đã được mở khóa</t>
+          <t>Bản Thiết Kế đã mở khóa</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Hệ thống Tổng Hợp không khả dụng</t>
+          <t>Hệ thống tổng hợp không khả dụng</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Không tìm thấy cấu hình Công Thức Tổng Hợp</t>
+          <t>Không tìm thấy cấu hình Công thức Tổng hợp</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Đã đạt số lần Tổng Hợp tối đa</t>
+          <t>Đã đạt số lần Tổng hợp tối đa</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Tổng Hợp không khả dụng</t>
+          <t>Không thể tổng hợp</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Không tìm thấy cấu hình Cấp Độ Tổng Hợp</t>
+          <t>Không tìm thấy cấu hình Cấp độ Tổng hợp</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Chưa đáp ứng điều kiện lên cấp</t>
+          <t>Điều kiện nâng cấp chưa đạt</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Công Thức Tổng Hợp đã được mở khóa</t>
+          <t>Công thức Tổng hợp đã mở khóa</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Nhân vật thử nghiệm, không thể ghép đội</t>
+          <t>Nhân vật thử nghiệm, không thể ghép cặp</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Hiện không thể dịch chuyển</t>
+          <t>Hiện tại bạn không thể dịch chuyển.</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Hiện không thể vào Chế Độ Đồng Đội</t>
+          <t>Hiện không thể tham gia Chế Độ Hợp Tác</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Không thể điều chỉnh đội hình trong trạng thái hiện tại</t>
+          <t>Không thể thay đổi đội hình ở trạng thái hiện tại</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Chuyển đội thất bại</t>
+          <t>Không thể đổi đội hình</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Chuyển nhân vật thất bại</t>
+          <t>Không thể đổi nhân vật</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Chuyển nhân vật thất bại</t>
+          <t>Không thể đổi nhân vật</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Nhân vật bị khóa</t>
+          <t>{CharacterName} đang bị khóa.</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Hiện không thể chuyển đổi</t>
+          <t>Không thể đổi nhân vật hiện tại</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Hiện không thể chuyển đổi</t>
+          <t>Không thể đổi nhân vật hiện tại</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Chưa thể chuyển đổi thuộc tính</t>
+          <t>Chưa thể chuyển đổi Thuộc tính</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Hiện không thể tham gia Co-op</t>
+          <t>Hiện không thể tham gia Chế Độ Hợp Tác</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Chủ phòng hiện không thể tham gia Co-op</t>
+          <t>Chủ trì hiện không thể tham gia Chế Độ Hợp Tác</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Tính năng bị khóa</t>
+          <t>Chức năng bị khóa</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Thực thể không hỗ trợ tính năng này</t>
+          <t>Hàm thực thể không được hỗ trợ</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Không tìm thấy lối vào Dungeon</t>
+          <t>Không tìm thấy lối vào Hầm</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Lối vào Dungeon không khớp</t>
+          <t>Lối vào Hầm không khớp</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Tính năng không khả dụng</t>
+          <t>Chức năng không khả dụng</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Email chưa được liên kết</t>
+          <t>Email Chưa Liên Kết</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Phần thưởng đã được nhận</t>
+          <t>Phần thưởng đã được nhận rồi</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Tính năng này không khả dụng trong chiến đấu trước lần đầu vượt ải</t>
+          <t>Tính năng này không khả dụng trong chiến đấu trước khi hoàn thành lần đầu.</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Tính năng này không khả dụng trong sự kiện này</t>
+          <t>Tính năng này không khả dụng trong sự kiện này.</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Tính năng không khả dụng</t>
+          <t>Chức năng không khả dụng</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Không khả dụng trong Dungeon này</t>
+          <t>Không khả dụng trong hầm ngục này</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Sự kiện chưa mở</t>
+          <t>Sự kiện chưa khả dụng</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Chưa nhận thưởng khảo sát</t>
+          <t>Phần thưởng khảo sát chưa nhận</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Không Storage Bag Configuration</t>
+          <t>Chưa Cấu Hình Túi Lưu Trữ</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Activated</t>
+          <t>Đã kích hoạt</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Đã đạt số Pin tối đa</t>
+          <t>Đã đạt số lượng Đinh tối đa</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Sương mù bản đồ đã mở khóa</t>
+          <t>Bản đồ sương mù đã được mở khóa</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Đội hình chưa xác định</t>
+          <t>Đội Hình Không Xác Định</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Resonator bị hạ gục không thể tham gia đội</t>
+          <t>Resonator bị hạ gục không thể tham gia đội hình</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Đội hình có quá nhiều Resonator</t>
+          <t>Đã đủ Resonator trong đội hình</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Resonator không tồn tại trong thiết lập đội trước trận đấu</t>
+          <t>Không thể thiết lập đội hình trước trận với Resonator không tồn tại</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Resonator không phù hợp trong thiết lập đội trước trận đấu</t>
+          <t>Resonator không phù hợp để thiết lập đội hình trước trận</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Số lượng nhân vật trước trận đấu không khớp</t>
+          <t>Số lượng Cộng Hưởng Giả trước trận đấu không khớp</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Loại Resonator không phù hợp trong thiết lập đội trước trận đấu</t>
+          <t>Loại Resonator không phù hợp với đội hình trước trận</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Thuộc tính Resonator không phù hợp trong thiết lập đội trước trận đấu</t>
+          <t>Thuộc tính Resonator không phù hợp với đội hình trước trận</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Resonator thử nghiệm không khả dụng trong thiết lập đội trước trận đấu hiện tại</t>
+          <t>Resonator Thử Nghiệm không khả dụng cho đội hình trước trận hiện tại</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Resonator thử nghiệm không phù hợp trong thiết lập đội trước trận đấu</t>
+          <t>Resonator Thử Nghiệm không phù hợp với đội hình trước trận</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Quá nhiều đội</t>
+          <t>Quá nhiều đội hình.</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Đã chọn Resonator bị hạ gục khi chỉnh sửa đội hình</t>
+          <t>Đã chọn Resonator bị hạ gục khi chỉnh đội hình</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Thiết lập đội mới đang trống</t>
+          <t>Thiết lập đội hình mới đang trống</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>ID đội vượt quá giới hạn</t>
+          <t>Số lượng thành viên Đội I vượt giới hạn</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Không thể xóa đội hiện tại</t>
+          <t>Không thể loại bỏ đội hiện tại</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Nhân vật không có trong danh sách đội khả dụng</t>
+          <t>Nhân vật không có trong danh sách đội hình khả dụng</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Loại nhân vật chuyển đổi không khớp 1</t>
+          <t>Loại Cộng Hưởng Giả thay thế không khớp 1</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Loại nhân vật chuyển đổi không khớp 2</t>
+          <t>Loại Cộng Hưởng Giả thay thế không khớp 2</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Loại nhân vật chuyển đổi không khớp 3</t>
+          <t>Loại Cộng Hưởng Giả thay thế không khớp 3</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Loại nhân vật chuyển đổi không xác định</t>
+          <t>Kiểu chuyển nhân vật không xác định</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Không thể chuyển đổi nhân vật hiện tại trong chế độ đơn người chơi</t>
+          <t>Không thể đổi nhân vật trong chế độ chơi đơn</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Danh sách nhân vật khả dụng trống khi cập nhật</t>
+          <t>Danh sách Cộng Hưởng Giả khả dụng chưa được cập nhật</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Không thể chuyển đổi từ nhân vật cốt truyện</t>
+          <t>Không thể chuyển đổi từ Nhân Vật Cốt Truyện</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Nhân vật cần chuyển đến không có trong danh sách khả dụng</t>
+          <t>Nhân vật muốn thay đổi không có trong danh sách khả dụng</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Không thể chuyển đổi liên tục đến cùng một nhân vật</t>
+          <t>Không thể chuyển đổi lại cùng một Nhân Vật</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>ID thực thể của nhân vật đã chuyển không tồn tại</t>
+          <t>ID thực thể của Nhân Vật đã chuyển không tồn tại</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Thực thể nhân vật đã chuyển không tồn tại</t>
+          <t>Thực thể Nhân Vật đã chuyển không tồn tại</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Không thể chuyển đến một Resonator đã bị hạ gục</t>
+          <t>Không thể chuyển sang Resonator đã bị đánh gục</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Điều chỉnh đội thất bại</t>
+          <t>Không thể điều chỉnh đội hình.</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Người chơi đã ở trong một đội</t>
+          <t>Người chơi đã có đội rồi</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Invalid Invite</t>
+          <t>Lời mời không hợp lệ</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Lỗi mời người chơi</t>
+          <t>Lỗi Mời Người Chơi</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Đội đã đầy</t>
+          <t>Đội đã đủ</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Dịch vụ tạo đội chưa sẵn sàng</t>
+          <t>Dịch vụ ghép đội chưa sẵn sàng.</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Người chơi đã ở trong đội, không thể tham gia lại</t>
+          <t>Người chơi đã ở trong đội, không thể tham gia lặp lại</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Người chơi không ở trong đội</t>
+          <t>Vận Mệnh Giả không thuộc đội nào</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Người chơi bị loại không ở trong đội</t>
+          <t>Người chơi bị loại không có trong đội</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Không có quyền giải tán đội</t>
+          <t>Không có quyền giải tán</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Nhân vật bị khóa cho đội</t>
+          <t>{CharacterName} bị khóa trong đội hình.</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Nhân vật đã ở trong đội</t>
+          <t>Nhân vật đã có trong đội</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Thế giới bạn đang tham gia không tồn tại</t>
+          <t>Thế giới cậu đang muốn tham gia không tồn tại</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Thế giới bạn đang tham gia không có trong BuildSettings</t>
+          <t>Thế giới mà cậu sắp bước vào không có trong BuildSettings đâu.</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Cảnh quan của thế giới bạn đang tham gia không tồn tại</t>
+          <t>Thế giới mà ngươi sắp bước vào không hề tồn tại cảnh này</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>ID dịch chuyển không tồn tại</t>
+          <t>Điểm dịch chuyển không tồn tại</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Điểm dịch chuyển chưa được kích hoạt</t>
+          <t>Điểm Dịch Chuyển chưa được kích hoạt</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Điểm dịch chuyển đã được kích hoạt</t>
+          <t>Điểm dịch chuyển đã kích hoạt</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Lỗi API GM dịch chuyển</t>
+          <t>Lỗi API Dịch chuyển GM</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Lỗi API GM dịch chuyển</t>
+          <t>Lỗi API Dịch chuyển GM</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>GM Teleport-to-Lối chơi không tồn tại</t>
+          <t>Không tìm thấy GM để dịch chuyển vào trò chơi</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Người chơi của GM Teleport-to-Lối chơi không tồn tại</t>
+          <t>Người chơi của GM không tồn tại</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Điểm Creation của GM Teleport-to-Lối chơi không tồn tại</t>
+          <t>Điểm Sáng Tạo của GM không tồn tại</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>GM Teleport-to-Lối chơi chuyển hướng đến khu vực khác</t>
+          <t>GM điều hướng Vận Mệnh Giả đến khu vực khác</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Thực thể Điểm dịch chuyển không tồn tại</t>
+          <t>Thực thể điểm dịch chuyển không tồn tại</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Phần thực thể Điểm dịch chuyển không tồn tại</t>
+          <t>Bộ phận thực thể điểm dịch chuyển không tồn tại</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Cấu hình phần thực thể Điểm dịch chuyển không khớp</t>
+          <t>Cấu hình bộ phận Điểm Dịch Chuyển không khớp</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Thử lại nhiều lần để vào khu vực</t>
+          <t>Thử lại để vào khu vực</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Hiện không thể hồi sinh nhân vật</t>
+          <t>Hiện không thể hồi sinh Cộng Hưởng Giả này</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Đã đạt số lần hồi sinh tối đa</t>
+          <t>Đã sử dụng hết số lần hồi sinh tối đa</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Matching</t>
+          <t>Đang ghép trận</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Hồ sơ ghép đội không tồn tại</t>
+          <t>Hồ sơ ghép trận không tồn tại</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Không tìm thấy kết quả ghép đội</t>
+          <t>Không tìm thấy kết quả phù hợp</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Đã xác nhận kết quả ghép đội</t>
+          <t>Xác nhận kết quả ghép trận</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Đội Dungeon đã tồn tại</t>
+          <t>Đội Tổ Tacet đã tồn tại</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Đội Dungeon không tồn tại</t>
+          <t>Đội Tổ Tacet không tồn tại</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Không ở trong đội</t>
+          <t>Không có trong đội</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Chủ thế giới không thể ở trạng thái Sẵn sàng</t>
+          <t>Chủ thế giới không thể sẵn sàng</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Đã đặt lại trạng thái Sẵn sàng</t>
+          <t>Trạng thái đã reset</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Nhân vật trùng lặp trong đội</t>
+          <t>Cùng một Cộng Hưởng Giả trong đội</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Không thể chỉnh sửa đội hình khi ở trạng thái Sẵn sàng</t>
+          <t>Không thể chỉnh sửa Đội hình khi đã ở trạng thái Sẵn Sàng</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Nhân vật đã có trong đội</t>
+          <t>Nhân vật đã được đặt trong đội</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Người chơi bị loại bỏ không có trong đội</t>
+          <t>Người chơi bị loại không có trong đội</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Không có quyền bắt đầu trận đấu</t>
+          <t>Không có quyền bắt đầu trận chiến</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>ID Dungeon không tồn tại</t>
+          <t>ID Hầm không tồn tại</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Bạn không có nhân vật được chỉ định để bắt đầu ghép đội</t>
+          <t>Bạn chưa chọn Nhân Vật chỉ định để bắt đầu ghép cặp</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Không thể ghép đội cho Dungeon đơn người chơi</t>
+          <t>Không thể ghép trận cho Dungeon Đơn Nhân</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Không thể bắt đầu ghép đội khi đang chờ người chơi khác vào cảnh</t>
+          <t>Không thể bắt đầu ghép trận khi đang đợi người chơi khác vào màn</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Không thể bắt đầu ghép đội khi đang vào thế giới khác</t>
+          <t>Không thể bắt đầu ghép trận khi đang ở Thế Giới khác</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Chưa hoàn thành</t>
+          <t>Vẫn chưa hoàn thiện</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Lối vào Dungeon bị khóa</t>
+          <t>Lối vào Hầm đã bị khóa</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Lối vào Dungeon không khả dụng</t>
+          <t>Lối vào Hầm không khả dụng</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Chưa đáp ứng yêu cầu cấp độ Dungeon</t>
+          <t>Chưa đủ cấp độ để vào Tổ Tacet</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Chưa đáp ứng yêu cầu giai đoạn SOL3 của Dungeon</t>
+          <t>Chưa đạt giai đoạn SOL-3 để vào Tổ Tacet</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Chưa hoàn thành nhiệm vụ yêu cầu của Dungeon</t>
+          <t>Chưa hoàn thành nhiệm vụ để vào Tổ Tacet</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Không thể vào Dungeon khi đang ghép đội</t>
+          <t>Không thể vào Dungeon khi đang ghép trận</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Không thể vào Dungeon khi đang vào Thế giới khác</t>
+          <t>Không thể vào Dungeon khi đang tiến vào Thế Giới khác</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Không thể vào Dungeon khi đang chờ người chơi khác vào Thế giới</t>
+          <t>Không thể vào Dungeon khi đang chờ người chơi khác tiến vào Thế Giới</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Loại Dungeon bạn đang vào không khớp</t>
+          <t>Loại Tacet Discord không phù hợp với Dungeon bạn đang vào</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Không có phần thưởng để nhận</t>
+          <t>Không có phần thưởng nào để xác nhận</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Matching</t>
+          <t>Đang ghép trận</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Không đang ghép đội</t>
+          <t>Không khớp</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Không tìm thấy máy chủ ghép đội phù hợp</t>
+          <t>Không tìm thấy máy chủ phù hợp</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Kết nối máy chủ ghép đội thất bại</t>
+          <t>Không thể kết nối với máy chủ ghép trận</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Không có thông tin đội ghép</t>
+          <t>Không tìm thấy thông tin đội hình phù hợp</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Đã xác nhận kết quả ghép đội</t>
+          <t>Xác nhận kết quả ghép trận</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Nhân vật bị khóa khi ghép đội</t>
+          <t>{CharacterName} bị khóa do đang ghép trận.</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Already Ready</t>
+          <t>Sẵn Sàng Rồi</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Cannot Unready</t>
+          <t>Không thể Hủy Sẵn Sàng</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Không thể đuổi thành viên khi không phải chủ đội</t>
+          <t>Không phải chủ phòng, không thể xóa</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Không thể ghép đội khi không phải chủ đội</t>
+          <t>Không thể ghép trận khi không phải chủ phòng</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Trạng thái ghép đội đã được thiết lập</t>
+          <t>Trạng thái ghép trận đã được thiết lập</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Người chơi không có trong đội đã ghép</t>
+          <t>Vận Mệnh Giả không thuộc đội đã ghép</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Không thể tìm thấy nhóm ghép trận</t>
+          <t>Không thể tải kho ghép trận phù hợp</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Người chơi đã trong nhóm ghép trận</t>
+          <t>Người chơi đã ở trong danh sách ghép trận</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Người chơi không trong nhóm ghép trận</t>
+          <t>Vận Mệnh Giả không trong danh sách ghép trận</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Không thể hủy khi Người chơi đã ở trong đội đã ghép trận</t>
+          <t>Không thể hủy khi người chơi đã vào đội ghép</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Đã xác nhận kết quả ghép trận</t>
+          <t>Xác nhận kết quả ghép trận</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Không tìm thấy đội đã ghép trận</t>
+          <t>Không tìm thấy đội hình phù hợp</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Không thể chỉnh sửa Đội hình khi ở trạng thái Sẵn sàng</t>
+          <t>Không thể chỉnh sửa Đội hình khi đã ở trạng thái Sẵn Sàng</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Không thể đặt nhiều Nhân vật làm non-host</t>
+          <t>Không thể đặt nhiều Cộng Hưởng Giả làm thành viên không chủ trì</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Không thể đặt Nhân vật đã có trong đội</t>
+          <t>Không thể đặt Cộng Hưởng Giả đã có trong đội</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Cannot Unready</t>
+          <t>Không thể Hủy Sẵn Sàng</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Không thể loại bỏ với tư cách non-World host</t>
+          <t>Không phải chủ thế giới, không thể xóa</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Không thể đặt trạng thái đội với tư cách non-World host</t>
+          <t>Không thể đặt trạng thái đội không phải chủ trì Thế giới</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Có Người chơi trong đội chưa Sẵn sàng</t>
+          <t>Thành viên trong đội chưa sẵn sàng</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Không thể bắt đầu Dungeon với tư cách non-World host</t>
+          <t>Không thể bắt đầu Dungeon nếu không phải chủ phòng thế giới</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Đội không vào Dungeon</t>
+          <t>Đội chưa vào được Dungeon.</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>ID Dungeon không tồn tại để ghép trận</t>
+          <t>ID Hầm không tồn tại để khớp</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Không thể ghép trận cho Dungeon đơn người chơi</t>
+          <t>Không thể ghép trận cho Dungeon Đơn Nhân</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Không thể ghép trận ở chế độ co-op</t>
+          <t>Không thể ghép trận ở chế độ Hợp Tác</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Không tìm thấy trò chuyện</t>
+          <t>Không tìm thấy cuộc trò chuyện</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Trò chuyện không khớp</t>
+          <t>Không khớp cuộc trò chuyện nào</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Không có Resonator nào khả dụng để chiến đấu</t>
+          <t>Không có Resonator nào sẵn sàng chiến đấu</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>ID cảnh tải không khớp</t>
+          <t>Lỗi tải cảnh: ID không khớp</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Sửa đổi chuỗi thông tin cơ bản không hợp lệ</t>
+          <t>Chuỗi thông tin cơ bản sửa đổi không hợp lệ</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Avatar bị khóa</t>
+          <t>Hóa Thân Đã Khóa</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Khung Avatar bị khóa</t>
+          <t>Khung Hóa Thân Đã Khóa</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Bạn không thể lấy thông tin cơ bản từ chính mình</t>
+          <t>Bạn không thể lấy được thông tin cơ bản từ chính bản thân mình.</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Thư không tồn tại</t>
+          <t>Thư này không tồn tại.</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Thư không chứa tệp đính kèm</t>
+          <t>Thư không có tệp đính kèm.</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Không còn chỗ trống trong Ba lô</t>
+          <t>Túi đồ đã đầy</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Chức năng thư không khả dụng</t>
+          <t>Chức năng thư chưa khả dụng</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Vượt quá dung lượng thư</t>
+          <t>Hộp thư đã đầy</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Vượt quá giới hạn số lượng nhận thư</t>
+          <t>Đã vượt quá số lượng giới hạn khi nhận thư</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Không tìm thấy cấu hình của vật phẩm đính kèm trong thư</t>
+          <t>Không tìm thấy cấu hình vật phẩm đính kèm trong thư</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Sản phẩm cửa hàng không tồn tại</t>
+          <t>Sản phẩm không tồn tại</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Không tìm thấy ID tiền tệ tương ứng</t>
+          <t>Không tìm thấy ID tiền tệ tương ứng.</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Chưa đáp ứng điều kiện mua hàng</t>
+          <t>Chưa đủ điều kiện mua</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Đã đạt cấp độ tối đa</t>
+          <t>Đã đạt cấp tối đa</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Giai đoạn SOL3 thấp hơn cấp tối thiểu yêu cầu để điều chỉnh</t>
+          <t>Pha SOL3 đang dưới mức tối thiểu cần thiết để điều chỉnh</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Thao tác đang trong thời gian hồi</t>
+          <t>Thao tác đang hồi chiêu</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Người chơi này đã có trong Danh sách chặn của bạn</t>
+          <t>Người chơi này đã có trong Danh sách Chặn của bạn</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Người chơi này không có trong Danh sách chặn của bạn</t>
+          <t>Người chơi này không có trong Danh sách Chặn của bạn</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Bạn đã bị chặn</t>
+          <t>Bạn đã bị chặn.</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Người chơi này đã có trong Danh sách bạn bè của bạn</t>
+          <t>Người chơi này đã có trong Danh sách Bạn bè của bạn</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Người chơi này không có trong Danh sách bạn bè của bạn</t>
+          <t>Người chơi này không có trong Danh sách Bạn bè của bạn</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Người chơi này có trong Yêu cầu kết bạn của bạn</t>
+          <t>Người chơi này đã gửi lời mời kết bạn cho bạn</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Danh sách bạn bè đã đầy</t>
+          <t>Danh sách bạn bè của bạn đã đầy</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Đã gửi yêu cầu</t>
+          <t>Đã gửi yêu cầu rồi</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Vượt quá giới hạn độ dài biệt danh bạn bè</t>
+          <t>Độ dài biệt danh bạn bè đã vượt quá giới hạn</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Đã đạt giới hạn yêu cầu kết bạn hàng ngày</t>
+          <t>Đã đạt giới hạn lời mời kết bạn hằng ngày</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Giao dịch được chỉ định không tồn tại</t>
+          <t>Vật phẩm trao đổi không tồn tại</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Giao dịch được chỉ định không thể sử dụng</t>
+          <t>Không thể sử dụng vật phẩm trao đổi này</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Sản phẩm được chỉ định không tồn tại</t>
+          <t>Sản phẩm không tồn tại</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Sản phẩm được chỉ định không thể sử dụng</t>
+          <t>Không thể sử dụng sản phẩm này</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Sản phẩm được chỉ định bị khóa</t>
+          <t>Sản phẩm này đang bị khóa</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Sản phẩm được chỉ định không khả dụng</t>
+          <t>Sản phẩm này hiện không khả dụng</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Số lượng mua không được vượt quá giới hạn mua</t>
+          <t>Số lượng mua không được vượt quá giới hạn</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Sản phẩm được chỉ định có thể mua trực tiếp</t>
+          <t>Có thể mua trực tiếp sản phẩm này</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Sản phẩm được chỉ định không thể mua trực tiếp</t>
+          <t>Không thể mua trực tiếp sản phẩm này</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Tab sản phẩm được chỉ định không thể sử dụng</t>
+          <t>Tab sản phẩm chỉ định không thể sử dụng</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Vật phẩm này không phải là vật phẩm sự kiện</t>
+          <t>Vật phẩm này không phải vật phẩm sự kiện.</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Không có vật phẩm sự kiện nào được trang bị</t>
+          <t>Chưa trang bị vật phẩm sự kiện nào</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Không có Pioneer Podcast khả dụng</t>
+          <t>Không có Podcast Tiên Phong nào khả dụng</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Pioneer Podcast bị khóa</t>
+          <t>Bản Tin Tiên Phong đang bị khóa</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Pioneer Podcast đã mở khóa</t>
+          <t>Bản Tin Tiên Phong đã mở khóa</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Đã nhận phần thưởng Pioneer Podcast</t>
+          <t>Đã nhận phần thưởng Bản Tin Tiên Phong</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Không thể mua lại Pioneer Podcast</t>
+          <t>Không thể mua lại Bản Tin Tiên Phong nhiều lần</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Pioneer Podcast không có phần thưởng chu kỳ</t>
+          <t>Bản Tin Tiên Phong không có phần thưởng chu kỳ</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Pioneer Podcast đã mở khóa</t>
+          <t>Bản Tin Tiên Phong đã mở khóa</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Không tìm thấy nhiệm vụ Pioneer Podcast</t>
+          <t>Không tìm thấy nhiệm vụ Podcast Tiên Phong</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Nhiệm vụ Pioneer Podcast chưa hoàn thành</t>
+          <t>Nhiệm vụ Podcast Tiên Phong chưa hoàn thành</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Không thể điền từ nối vào từ</t>
+          <t>Từ nối không thể điền vào chỗ trống</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Không tìm thấy từ trò chuyện</t>
+          <t>Không tìm thấy nội dung trò chuyện</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Không phải thực thể Chat</t>
+          <t>Không Phải Thực Thể Trò Chuyện</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Đã đạt giới hạn tạo Chat</t>
+          <t>Đã đạt giới hạn tạo cuộc trò chuyện</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Nội dung Chat không được để trống</t>
+          <t>Nội dung trò chuyện không được để trống</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Thực thể Chat không tồn tại</t>
+          <t>Thực thể trò chuyện không tồn tại</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Đã đạt giới hạn bình luận hàng ngày</t>
+          <t>Đã đạt giới hạn bình luận hằng ngày</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Liked</t>
+          <t>Đã thích</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Disliked</t>
+          <t>Không ưa thích</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Không có vật phẩm Chat</t>
+          <t>Không có vật phẩm trò chuyện</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Tạo Chat đã bị khóa</t>
+          <t>Tạo Trò Chuyện đã bị khóa</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Khách không thể tạo Chat</t>
+          <t>Khách không thể tạo Trò Chuyện</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Chat hiện tại đã được đặt hiển thị</t>
+          <t>Tin nhắn hiện tại được hiển thị</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Chat hiện tại đã được đặt ẩn</t>
+          <t>Tin nhắn hiện tại được ẩn đi</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24654,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Đã đạt giới hạn thích</t>
+          <t>Như kiểu đã đạt giới hạn</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Lỗi Túi đồ nhiệm vụ</t>
+          <t>Lỗi Túi Đồ Nhiệm Vụ</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Trạng thái tiến trình nhiệm vụ không thể nhận</t>
+          <t>Trạng thái tiến trình nhiệm vụ không thể chấp nhận</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Cấu hình tiến trình nhiệm vụ không chính xác</t>
+          <t>Cấu hình tiến trình nhiệm vụ sai</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Dữ liệu tiến trình nhiệm vụ không chính xác</t>
+          <t>Dữ liệu tiến trình nhiệm vụ sai</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Không thể nhận loại nhiệm vụ này</t>
+          <t>Không thể nhận nhiệm vụ loại này</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Nút nhiệm vụ chưa được kích hoạt</t>
+          <t>Điểm nhiệm vụ chưa được kích hoạt</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Nhiệm vụ không tìm thấy ID hành vi này</t>
+          <t>Không tìm thấy Id hành vi nhiệm vụ này</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Không tìm thấy nút nhiệm vụ</t>
+          <t>Không tìm thấy điểm nhiệm vụ</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Trạng thái nhiệm vụ không phải đang tiến hành</t>
+          <t>Nhiệm vụ chưa được tiến hành</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Dữ liệu nút nhiệm vụ không chính xác</t>
+          <t>Dữ liệu nút nhiệm vụ sai</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Loại nhiệm vụ này không thể nộp từ giao diện người dùng</t>
+          <t>Loại nhiệm vụ này không thể nộp từ giao diện chính</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Đã nhận nhiệm vụ</t>
+          <t>Nhiệm vụ đã tiếp nhận</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Không đủ tài nguyên nhiệm vụ yêu cầu</t>
+          <t>Không đủ tài nguyên cần thiết cho nhiệm vụ</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Yêu cầu chiếm dụng tài nguyên không hợp lệ</t>
+          <t>Yêu cầu chiếm giữ tài nguyên không hợp lệ</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Không tìm thấy danh sách tài nguyên cần chiếm dụng</t>
+          <t>Không tìm thấy danh sách tài nguyên cần chiếm giữ</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Không thể nhận loại nhiệm vụ này trong Chế độ Co-op</t>
+          <t>Nhiệm vụ này không thể nhận trong Chế độ Hợp tác.</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26334,7 +26334,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Không thể nhận nhiệm vụ đã bị hủy</t>
+          <t>Không thể nhận nhiệm vụ đã bị phá hủy</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Không tìm thấy nút</t>
+          <t>Không tìm thấy điểm nút</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Nút chưa được kích hoạt</t>
+          <t>Điểm nút chưa kích hoạt</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Không phải là nút nhiệm vụ phụ</t>
+          <t>Không phải nút nhiệm vụ phụ</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Không phải là nút nhiệm vụ phụ</t>
+          <t>Không phải nút nhiệm vụ phụ</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Nút không tìm thấy hành vi này</t>
+          <t>Không tìm thấy hành vi này tại điểm nút</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Hành vi của nút này đã hoàn thành</t>
+          <t>Hoạt động nút này đã hoàn tất</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Hành vi nhận vật phẩm nhiệm vụ không đủ không gian trong ba lô</t>
+          <t>Không đủ không gian trong túi đồ để nhận vật phẩm nhiệm vụ</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Điều kiện tiên quyết chưa được đáp ứng</t>
+          <t>Điều kiện tiên quyết chưa đạt</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Không tìm thấy dữ liệu của vật phẩm cần giao</t>
+          <t>Không tìm thấy dữ liệu vật phẩm cần giao</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Không phải là nút thất bại</t>
+          <t>Không phải nút thất bại</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27384,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Không có cấu hình nào có thể hủy</t>
+          <t>Không có cấu hình nào là vô giá trị.</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Không thể khôi phục trạng thái nhiệm vụ hiện tại</t>
+          <t>Không thể hoàn tác trạng thái nhiệm vụ hiện tại</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Không tìm thấy ID thực thể tương tác</t>
+          <t>Không tìm thấy thực thể tương tác</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Không thể yêu cầu khôi phục nhiều lần</t>
+          <t>Không thể yêu cầu khôi phục liên tục</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Không thể tiến triển ở trạng thái tạm dừng</t>
+          <t>Không thể tiến triển khi đang bị treo</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Không phải là thực thể có thể thu thập</t>
+          <t>Không phải thứ có thể thu thập được</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Không phải là thực thể có thể thu thập</t>
+          <t>Không phải thứ có thể thu thập được</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Không tìm thấy gameplay đang chạy</t>
+          <t>Không tìm thấy gameplay nào đang chạy</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Không tìm thấy thực thể tương tác</t>
+          <t>Không tìm thấy thực thể tương tác nào</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>ConfigId của thực thể không tìm thấy gameplay Id</t>
+          <t>Không tìm thấy gameplay Id của Entity ConfigId</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Lối chơi chưa được tạo</t>
+          <t>Chưa tạo trò chơi</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Phần thưởng gameplay đã được nhận</t>
+          <t>Đã nhận thưởng trò chơi</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Lối chơi không thể tương tác</t>
+          <t>Mục tiêu không thể tương tác</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Lối chơi không tìm thấy người chơi</t>
+          <t>Không tìm thấy người chơi trong gameplay</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Chưa hoàn thành</t>
+          <t>Vẫn chưa hoàn thiện</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Không thể nhận thưởng gameplay</t>
+          <t>Không thể nhận thưởng trò chơi</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Lối chơi không chờ đợi</t>
+          <t>Trò chơi không ở trạng thái chờ</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Câu chuyện không tồn tại</t>
+          <t>Câu chuyện ấy không hề tồn tại.</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Không có hội thoại</t>
+          <t>Không có lời thoại</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Không có tùy chọn</t>
+          <t>Không có lựa chọn</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Tùy chọn sai</t>
+          <t>Lựa chọn sai rồi.</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Không thể tương tác trong Chế độ Đồng đội</t>
+          <t>Không thể tương tác trong Chế Độ Đồng Đội</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Vượt quá giới hạn yêu cầu phần thưởng nhiệm vụ</t>
+          <t>Đã vượt quá giới hạn nhận thưởng nhiệm vụ</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Bạn đã nhận thưởng nhiệm vụ rồi</t>
+          <t>Ngươi đã nhận phần thưởng nhiệm vụ rồi</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Không tìm thấy cấu hình game</t>
+          <t>Không tìm thấy cấu hình trò chơi</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Không có xúc xắc khả dụng</t>
+          <t>Không có xúc xắc nào khả dụng</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Không có thưởng Pad khả dụng</t>
+          <t>Không có phần thưởng bệ nhảy nào khả dụng</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Vượt quá giới hạn yêu cầu phần thưởng game</t>
+          <t>Đã vượt quá giới hạn yêu cầu phần thưởng trò chơi</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Game chưa hoàn thành</t>
+          <t>Chưa hoàn thành trò chơi</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Đã nhận thưởng game rồi</t>
+          <t>Đã nhận phần thưởng trò chơi</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Game bị khóa</t>
+          <t>Trò chơi đã bị khóa</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Lỗi số lượng xúc xắc</t>
+          <t>Lỗi số xúc xắc</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30464,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Invalid User ID</t>
+          <t>ID Người dùng không hợp lệ</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Người chơi không có trong cảnh</t>
+          <t>Vận Mệnh Giả không có mặt trong cảnh</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Vật phẩm rơi không tồn tại</t>
+          <t>Không tồn tại vật phẩm thả</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Thành phần vật phẩm rơi không tồn tại</t>
+          <t>Không tồn tại thành phần thả</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Lỗi sở hữu vật phẩm rơi</t>
+          <t>Lỗi sở hữu vật phẩm thả</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Người chơi đang ở trong cảnh</t>
+          <t>Vận Mệnh Giả đã có mặt trong cảnh</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Mời vào cảnh thất bại</t>
+          <t>Mời cảnh thất bại</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Đội đã đầy</t>
+          <t>Đội đã đủ người.</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Người chơi bị loại không có trong cảnh</t>
+          <t>Người chơi bị loại không còn trong cảnh này.</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Không thể loại bỏ người chơi đang trong dungeon</t>
+          <t>Không thể xóa người chơi đang ở trong hầm ngục</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Người mời đang ở cảnh của người chơi khác</t>
+          <t>Người mời đang ở trong cảnh của người chơi khác</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Không thể mời trong thế giới của người chơi khác</t>
+          <t>Không thể mời vào thế giới của người chơi khác</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Lỗi đánh dấu trở về</t>
+          <t>Lỗi trả dấu</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>ID cảnh rời đi không khớp</t>
+          <t>Lỗi không khớp ID cảnh rời đi</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Đã có đội hình trước trận đấu</t>
+          <t>Đã thiết lập đội hình trước trận đấu</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Không có đội hình trước trận đấu</t>
+          <t>Đội hình trước trận đấu không tồn tại</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Không đủ quyền để tạo thiết lập đội trước trận đấu</t>
+          <t>Không đủ quyền để tạo đội hình trước trận đấu.</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Không đủ quyền mời trong thiết lập đội trước trận đấu</t>
+          <t>Quyền mời thiết lập đội hình trước trận chưa đủ</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32354,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Người chơi được mời thiết lập đội trước trận đấu không có trong khu vực</t>
+          <t>Người chơi được mời không có mặt trong cảnh này</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Người chơi được mời thiết lập đội trước trận đấu đang ở dungeon khác</t>
+          <t>Người chơi được mời đang ở trong hầm khác</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Người chơi đang trong thiết lập đội trước trận đấu</t>
+          <t>Đang trong giao diện đội hình trước trận đấu</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Người chơi không có trong thiết lập đội trước trận đấu</t>
+          <t>Người chơi không ở trong giao diện đội hình trước trận đấu</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Trạng thái sẵn sàng của người chơi bị trùng lặp</t>
+          <t>Trạng thái sẵn sàng của người chơi đã được thiết lập lại</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Người chơi bị loại không có trong khu vực</t>
+          <t>Người chơi bị loại không còn trong cảnh này.</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Không đủ quyền để loại bỏ</t>
+          <t>Không đủ quyền để xóa.</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Bạn đang gửi lời mời quá thường xuyên</t>
+          <t>Cậu gửi lời mời nhiều quá đấy</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>ID dungeon không khớp</t>
+          <t>ID Hầm không khớp</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32984,7 +32984,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Đội trưởng không thể rời khỏi trong quá trình thiết lập đội</t>
+          <t>Trưởng đội không thể rời đi trong lúc thiết lập đội.</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33054,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Không thể chỉnh sửa đội hình khi ở trạng thái Sẵn sàng</t>
+          <t>Không thể chỉnh sửa Đội hình khi đã ở trạng thái Sẵn Sàng</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Chỉ đội trưởng mới có thể giải tán thiết lập đội trước trận đấu</t>
+          <t>Chỉ đội trưởng mới có thể giải tán đội hình trước trận đấu</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Lỗi chỉ số Resonator khi chuyển đổi</t>
+          <t>Lỗi chỉ số Resonator</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Không thể chuyển đổi sang Resonator của người chơi khác</t>
+          <t>Không thể chuyển sang Resonator của người chơi khác</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Resonator được chuyển đổi không tồn tại</t>
+          <t>Resonator được chọn không tồn tại</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Tính năng này không khả dụng trong khu vực này</t>
+          <t>Tính năng này không khả dụng trong cảnh này.</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Vật phẩm này không khả dụng trong khu vực này</t>
+          <t>Vật phẩm này không khả dụng trong cảnh này.</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Resonator đã triển khai bị trùng lặp</t>
+          <t>Triệu hồi Resonator liên tục</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Shield không tồn tại</t>
+          <t>Thực thể khiên không tồn tại</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Shield unique Id đã tồn tại</t>
+          <t>ID khiên độc nhất của Khiên đã tồn tại</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Thực thể thay đổi giá trị Shield không tồn tại</t>
+          <t>Không tìm thấy thực thể thay đổi giá trị khiên</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Shield unique Id để thay đổi giá trị không tồn tại</t>
+          <t>ID khiên duy nhất để thay đổi giá trị khiên không tồn tại</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Thực thể loại bỏ lá chắn không tồn tại</t>
+          <t>Không tìm thấy thực thể loại bỏ khiên</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Id lá chắn duy nhất để loại bỏ lá chắn không tồn tại</t>
+          <t>ID khiên duy nhất để loại bỏ khiên không tồn tại</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Thực thể điều chỉnh Độ rung không tồn tại</t>
+          <t>Không tìm thấy thực thể điều chỉnh Sức Mạnh Rung Động</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Thực thể cảnh không tồn tại</t>
+          <t>Thực thể trong cảnh không tồn tại</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Abandoned</t>
+          <t>Đã hủy</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Triển khai trùng lặp</t>
+          <t>Triển khai lại</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34454,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Tải dữ liệu cảnh thất bại</t>
+          <t>Không tải được dữ liệu cảnh</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Xác minh dữ liệu tạo của người chơi thất bại</t>
+          <t>Không thể xác minh dữ liệu tạo nhân vật của người chơi</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34594,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Điểm tạo đã tồn tại</t>
+          <t>Điểm sáng tạo tồn tại.</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Điểm tạo không tồn tại</t>
+          <t>Điểm sáng tạo không tồn tại.</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Quyền tạo điểm đã được người chơi khác sở hữu</t>
+          <t>Quyền sử dụng điểm sáng tạo đã thuộc về người chơi khác.</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Không có quyền tạo</t>
+          <t>Không có quyền tạo mới</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Đã đạt số lần tạo tối đa</t>
+          <t>Đã đạt số lần chế tạo tối đa</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Chưa đáp ứng điều kiện tạo</t>
+          <t>Điều kiện sáng tạo chưa đạt</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Lỗi tần suất làm mới tạo</t>
+          <t>Lỗi tốc độ làm mới sáng tạo.</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Cấu hình tạo không tồn tại</t>
+          <t>Cấu hình sáng tạo không tồn tại.</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Thực thể duy nhất không thể tạo hai lần</t>
+          <t>Thực thể duy nhất không thể được tạo ra hai lần.</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35434,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Cấu hình gameplay cơ sở huấn luyện không tồn tại</t>
+          <t>Cấu hình lối chơi cơ sở huấn luyện không tồn tại</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
